--- a/data/trans_dic/IP44C$recibos_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 21,03</t>
+          <t>7,93; 20,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 16,46</t>
+          <t>4,8; 17,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 16,67</t>
+          <t>7,67; 16,92</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 15,58</t>
+          <t>7,57; 15,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 16,14</t>
+          <t>7,8; 16,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 14,39</t>
+          <t>8,53; 14,52</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 13,21</t>
+          <t>5,68; 13,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,09</t>
+          <t>4,32; 11,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 10,74</t>
+          <t>5,66; 10,86</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,13</t>
+          <t>4,42; 10,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 11,99</t>
+          <t>5,93; 11,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,56</t>
+          <t>5,43; 9,96</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,0</t>
+          <t>6,98; 10,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,96</t>
+          <t>7,24; 10,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 10,42</t>
+          <t>7,63; 10,34</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7637</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5915</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13552</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4516; 11902</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2932; 10617</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9058; 19970</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>17047</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20175</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37221</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>11808; 24850</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13885; 29222</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28507; 48493</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15247</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14590</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29837</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9651; 22934</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8789; 22635</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21160; 40589</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>18189</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25593</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>43783</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11891; 28447</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17877; 35755</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30950; 56795</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>58120</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>66273</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124393</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>45492; 71648</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>53846; 81387</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>106580; 144431</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$recibos_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,93; 20,89</t>
+          <t>7,84; 21,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 17,39</t>
+          <t>4,56; 16,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 16,92</t>
+          <t>7,6; 16,39</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,94</t>
+          <t>7,5; 16,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 16,41</t>
+          <t>7,55; 15,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 14,52</t>
+          <t>8,5; 14,44</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 13,49</t>
+          <t>5,63; 13,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 11,12</t>
+          <t>4,38; 10,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,86</t>
+          <t>5,64; 10,59</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 10,57</t>
+          <t>4,09; 10,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,87</t>
+          <t>5,72; 11,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,96</t>
+          <t>5,75; 9,83</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,99</t>
+          <t>6,75; 11,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,94</t>
+          <t>7,25; 11,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,34</t>
+          <t>7,56; 10,33</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4516; 11902</t>
+          <t>4467; 12091</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2932; 10617</t>
+          <t>2784; 10068</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9058; 19970</t>
+          <t>8974; 19347</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11808; 24850</t>
+          <t>11693; 24953</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13885; 29222</t>
+          <t>13449; 27872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28507; 48493</t>
+          <t>28383; 48218</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9651; 22934</t>
+          <t>9565; 22376</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8789; 22635</t>
+          <t>8912; 22152</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21160; 40589</t>
+          <t>21078; 39573</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11891; 28447</t>
+          <t>11016; 27516</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17877; 35755</t>
+          <t>17246; 36038</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30950; 56795</t>
+          <t>32798; 56083</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45492; 71648</t>
+          <t>43995; 71708</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53846; 81387</t>
+          <t>53950; 82476</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106580; 144431</t>
+          <t>105592; 144159</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$recibos_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,84; 21,22</t>
+          <t>4,38; 17,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 16,49</t>
+          <t>7,41; 20,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 16,39</t>
+          <t>7,77; 17,03</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 16,0</t>
+          <t>7,41; 16,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,65</t>
+          <t>7,48; 16,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 14,44</t>
+          <t>8,56; 14,65</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 13,16</t>
+          <t>4,66; 11,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,88</t>
+          <t>6,14; 14,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,59</t>
+          <t>6,15; 11,42</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,22</t>
+          <t>6,65; 13,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,96</t>
+          <t>5,24; 11,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,83</t>
+          <t>6,54; 11,04</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,0</t>
+          <t>7,62; 11,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,08</t>
+          <t>7,88; 12,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,33</t>
+          <t>8,1; 10,99</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>11798</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4467; 12091</t>
+          <t>2198; 8873</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2784; 10068</t>
+          <t>3825; 10623</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8974; 19347</t>
+          <t>7909; 17344</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>33687</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11693; 24953</t>
+          <t>11331; 24603</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13449; 27872</t>
+          <t>10729; 23420</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28383; 48218</t>
+          <t>25351; 43396</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15247</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14590</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29837</t>
+          <t>30959</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9565; 22376</t>
+          <t>8934; 22649</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8912; 22152</t>
+          <t>10528; 24019</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21078; 39573</t>
+          <t>22330; 41468</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>27119</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25593</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43783</t>
+          <t>47231</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11016; 27516</t>
+          <t>19174; 38372</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17246; 36038</t>
+          <t>13133; 28564</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32798; 56083</t>
+          <t>35242; 59462</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58120</t>
+          <t>64371</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124393</t>
+          <t>123676</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43995; 71708</t>
+          <t>52080; 79556</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53950; 82476</t>
+          <t>48592; 74042</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>105592; 144159</t>
+          <t>105345; 142901</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$recibos_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,38; 17,67</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7,41; 20,58</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7,77; 17,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7,41; 16,09</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7,48; 16,33</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8,56; 14,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4,66; 11,82</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6,14; 14,01</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>6,15; 11,42</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>6,65; 13,31</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5,24; 11,4</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6,54; 11,04</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>7,62; 11,65</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7,88; 12,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8,1; 10,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.103664427299376</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1277192334744245</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1158556369266597</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5206</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6592</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11798</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.04375509108289397</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.07410698907480134</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.07766023983598702</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2198; 8873</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3825; 10623</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7909; 17344</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1766716156612135</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.2058264268784742</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1703145277228227</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1124720921207106</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1149994806493475</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1136951533104217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>17198</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>16489</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33687</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.07410015787654314</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.07482702287535345</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.08556059182138226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>11331; 24603</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10729; 23420</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>25351; 43396</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1608999971806127</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1633409639667782</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1464649847981787</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.07749736828204686</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.09398180468731038</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.08528189326021489</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>14848</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16112</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>30959</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.04663186077715097</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.06141001966665716</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.06151208779665523</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>8934; 22649</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>10528; 24019</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22330; 41468</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1182137430994989</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.14010647646679</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1142281344589915</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.09404482241609746</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.08029568671278525</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.08765356231113951</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>27119</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>20112</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47231</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.06649138961323096</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.05243265179322782</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.06540394462453004</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>19174; 38372</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>13133; 28564</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>35242; 59462</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1330679718076424</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1140356309998658</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1103513881712329</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.09423580116271311</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.0961323140674791</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.09513578263351097</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>64371</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>59305</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>123676</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.07624276757825967</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.07876727035487753</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.08103488366238508</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>52080; 79556</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>48592; 74042</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>105345; 142901</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1164652119498361</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1200224591607166</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.109924892575159</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>5206</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>6592</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>11798</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2198</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>3825</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>7909</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>8873</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>10623</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>17344</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>17198</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>16489</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>33687</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>11331</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>10729</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>25351</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>24603</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>23420</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>43396</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>14848</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>16112</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>30959</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>8934</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>10528</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>22330</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>22649</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>24019</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>41468</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>27119</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>20112</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>47231</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>19174</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>13133</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>35242</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>38372</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>28564</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>59462</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>64371</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>59305</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>123676</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>52080</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>48592</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>105345</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>79556</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>74042</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>142901</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>